--- a/test_upload.xlsx
+++ b/test_upload.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Calls" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,129 +413,88 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:E3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>dietician_id</t>
+          <t>dietician_name</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>dietician_name</t>
+          <t>patient_id</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>patient_id</t>
+          <t>patient_name</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>patient_name</t>
+          <t>appointment_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>appointment_id</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>call_datetime</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
           <t>recording_url</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>call_duration_seconds</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1</t>
+          <t>Dr. Raj Kumar</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Dr. Test</t>
+          <t>P001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>p1</t>
+          <t>Patient One</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Patient Test 1</t>
+          <t>APT001</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>apt1</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-07-10 10:00:00</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>https://example.com/call1.mp3</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
-        <v>1200</v>
+          <t>https://dashboard.hellotubelight.com/recording//bajajfinservt//2026-06/06937a25-f363-444c-912a-e31d43ad1804.mp3</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>d2</t>
+          <t>Dr. Priya Singh</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Dr. Test 2</t>
+          <t>P002</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>p2</t>
+          <t>Patient Two</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Patient Test 2</t>
+          <t>APT002</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>apt2</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-07-10 11:00:00</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>https://example.com/call2.mp3</t>
-        </is>
-      </c>
-      <c r="H3" t="n">
-        <v>900</v>
+          <t>https://dashboard.hellotubelight.com/recording//bajajfinservt//2026-06/6b7898ac-42fc-44e9-8328-8cec7d5e43ad.mp3</t>
+        </is>
       </c>
     </row>
   </sheetData>
